--- a/data/WP18/WP18_sachgebiete_AfD_zeitreihe.xlsx
+++ b/data/WP18/WP18_sachgebiete_AfD_zeitreihe.xlsx
@@ -1769,13 +1769,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{434F8FAD-C951-4DAA-959F-4B9E0DB0D49F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32EFE38D-302A-49B7-B416-A38D59CD35F2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{203A18C3-6C64-4D33-BB66-315205F29345}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA11DE1A-15F5-47AB-801B-B4FD6D4FD759}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FCB44CF-8B95-41A1-B429-AB508A49338A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{822406AD-6FE2-4C27-B8F8-87CC84195078}"/>
 </file>
--- a/data/WP18/WP18_sachgebiete_AfD_zeitreihe.xlsx
+++ b/data/WP18/WP18_sachgebiete_AfD_zeitreihe.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">periode</t>
   </si>
@@ -74,15 +74,15 @@
     <t xml:space="preserve">Bergbau, Bodenschätze</t>
   </si>
   <si>
+    <t xml:space="preserve">Politische Kräfte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesundheitseinrichtungen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Justizvollzug</t>
   </si>
   <si>
-    <t xml:space="preserve">Politische Kräfte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesundheitseinrichtungen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kommunale Angelegenheiten</t>
   </si>
   <si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t xml:space="preserve">Gesundheitsschutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natur</t>
   </si>
   <si>
     <t xml:space="preserve">Kunst, Kultur</t>
@@ -514,7 +517,7 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -531,13 +534,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
@@ -554,7 +557,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -954,7 +957,7 @@
         <v>14</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
         <v>4</v>
@@ -1023,7 +1026,7 @@
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25" t="n">
         <v>7</v>
@@ -1040,13 +1043,13 @@
         <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
         <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G26" t="n">
         <v>16</v>
@@ -1454,13 +1457,13 @@
         <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -1477,7 +1480,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E45" t="n">
         <v>11</v>
@@ -1494,13 +1497,13 @@
         <v>46054</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C46" t="n">
         <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E46" t="n">
         <v>9</v>
@@ -1769,13 +1772,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32EFE38D-302A-49B7-B416-A38D59CD35F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D598ABA-3469-463E-B054-8DCA45FBF47D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA11DE1A-15F5-47AB-801B-B4FD6D4FD759}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D9A79AA-9907-4BCE-881C-43E1F5A4C40A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{822406AD-6FE2-4C27-B8F8-87CC84195078}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3E62690-B756-4DEA-A570-9BF354758F2E}"/>
 </file>
--- a/data/WP18/WP18_sachgebiete_AfD_zeitreihe.xlsx
+++ b/data/WP18/WP18_sachgebiete_AfD_zeitreihe.xlsx
@@ -1772,13 +1772,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D598ABA-3469-463E-B054-8DCA45FBF47D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{610C47CD-D1E8-43E5-A7F1-B781E2AEB487}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D9A79AA-9907-4BCE-881C-43E1F5A4C40A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4120B9F-7764-4892-85E3-CF5345630AC3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3E62690-B756-4DEA-A570-9BF354758F2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B87AD4B-2099-45B2-B458-49CE08A5F300}"/>
 </file>